--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 05/NKSX_TG102LE(8686)_SL55_180526.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 05/NKSX_TG102LE(8686)_SL55_180526.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Nhập kho\Tháng 05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12A0D461-B651-4DC5-92FB-AAC5CEDF63C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D8B7F7E-15F2-4D80-9616-7DE0E68131A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -103,9 +103,6 @@
     <t>Họ và tên người đề nghị: Nguyễn Minh Tùng</t>
   </si>
   <si>
-    <t>Hà Nội, ngày 18 tháng 05 năm 2026</t>
-  </si>
-  <si>
     <t>TG102LE-4G(8686)</t>
   </si>
   <si>
@@ -113,9 +110,6 @@
   </si>
   <si>
     <t>Nhập kho thành phẩm TG102LE-4G (Version 8686)</t>
-  </si>
-  <si>
-    <t>Lô 1/2026 TG102LE-4G</t>
   </si>
   <si>
     <t>Phòngban/ Bộ phận: PKT/ Bảo hành - Sản xuất</t>
@@ -294,6 +288,12 @@
   <si>
     <t>5 IMEI nhập kho 
 16/-5/2026</t>
+  </si>
+  <si>
+    <t>Lô 2/2026 TG102LE-4G</t>
+  </si>
+  <si>
+    <t>Hà Nội, ngày 16 tháng 05 năm 2026</t>
   </si>
 </sst>
 </file>
@@ -678,68 +678,68 @@
     <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1173,66 +1173,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="42" t="s">
+      <c r="B1" s="32"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="44"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="42"/>
     </row>
     <row r="2" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="36"/>
-      <c r="B2" s="37"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="45" t="s">
+      <c r="A2" s="34"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="46"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="44"/>
     </row>
     <row r="3" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="36"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="45" t="s">
+      <c r="A3" s="34"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="46"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="44"/>
     </row>
     <row r="4" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="39"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="47" t="s">
+      <c r="A4" s="37"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="48"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="46"/>
     </row>
     <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="31"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="32"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="30"/>
     </row>
     <row r="6" spans="1:8" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
@@ -1245,12 +1245,12 @@
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
       <c r="H6" s="14" t="s">
-        <v>25</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="9"/>
@@ -1303,10 +1303,10 @@
         <v>1</v>
       </c>
       <c r="B10" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="21" t="s">
         <v>26</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>27</v>
       </c>
       <c r="D10" s="22">
         <v>55</v>
@@ -1314,10 +1314,10 @@
       <c r="E10" s="21"/>
       <c r="F10" s="17"/>
       <c r="G10" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -1341,40 +1341,40 @@
       <c r="H12" s="3"/>
     </row>
     <row r="13" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="28" t="s">
+      <c r="A13" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28" t="s">
+      <c r="B13" s="47"/>
+      <c r="C13" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28" t="s">
+      <c r="D13" s="47"/>
+      <c r="E13" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28" t="s">
+      <c r="F13" s="47"/>
+      <c r="G13" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="28"/>
+      <c r="H13" s="47"/>
     </row>
     <row r="14" spans="1:8" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="29" t="s">
+      <c r="A14" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29" t="s">
+      <c r="B14" s="48"/>
+      <c r="C14" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29" t="s">
+      <c r="D14" s="48"/>
+      <c r="E14" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29" t="s">
+      <c r="F14" s="48"/>
+      <c r="G14" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="29"/>
+      <c r="H14" s="48"/>
     </row>
     <row r="15" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="13"/>
@@ -1427,22 +1427,22 @@
       <c r="H19" s="13"/>
     </row>
     <row r="20" spans="1:8" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28" t="s">
+      <c r="B20" s="47"/>
+      <c r="C20" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28" t="s">
+      <c r="D20" s="47"/>
+      <c r="E20" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28" t="s">
+      <c r="F20" s="47"/>
+      <c r="G20" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="H20" s="28"/>
+      <c r="H20" s="47"/>
     </row>
     <row r="21" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="22" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -1468,24 +1468,24 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C20:D20"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="D1:H1"/>
     <mergeCell ref="D3:H3"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="D4:H4"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G14:H14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -1507,19 +1507,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C1" s="26" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A2" s="50"/>
       <c r="B2" s="25" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1527,10 +1527,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1538,10 +1538,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1549,10 +1549,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1560,10 +1560,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1571,10 +1571,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="B8" s="24"/>
       <c r="C8" s="24" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="B9" s="24"/>
       <c r="C9" s="24" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="B10" s="24"/>
       <c r="C10" s="24" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="B11" s="24"/>
       <c r="C11" s="24" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="B12" s="24"/>
       <c r="C12" s="24" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="B13" s="24"/>
       <c r="C13" s="24" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="B14" s="24"/>
       <c r="C14" s="24" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B15" s="24"/>
       <c r="C15" s="24" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="B16" s="24"/>
       <c r="C16" s="24" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="B17" s="24"/>
       <c r="C17" s="24" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="B18" s="24"/>
       <c r="C18" s="24" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B19" s="24"/>
       <c r="C19" s="24" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="B20" s="24"/>
       <c r="C20" s="24" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="B21" s="24"/>
       <c r="C21" s="24" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="B22" s="24"/>
       <c r="C22" s="24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="B23" s="24"/>
       <c r="C23" s="24" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="B24" s="24"/>
       <c r="C24" s="24" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="B25" s="24"/>
       <c r="C25" s="24" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="B26" s="24"/>
       <c r="C26" s="24" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="B27" s="24"/>
       <c r="C27" s="24" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="B28" s="24"/>
       <c r="C28" s="24" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B29" s="24"/>
       <c r="C29" s="24" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="B30" s="24"/>
       <c r="C30" s="24" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="B31" s="24"/>
       <c r="C31" s="24" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="B32" s="24"/>
       <c r="C32" s="24" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B33" s="24"/>
       <c r="C33" s="24" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="B34" s="24"/>
       <c r="C34" s="24" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="B35" s="24"/>
       <c r="C35" s="24" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="B36" s="24"/>
       <c r="C36" s="24" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="B37" s="24"/>
       <c r="C37" s="24" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="B38" s="24"/>
       <c r="C38" s="24" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="B39" s="24"/>
       <c r="C39" s="24" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B40" s="24"/>
       <c r="C40" s="24" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="B41" s="24"/>
       <c r="C41" s="24" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="B42" s="24"/>
       <c r="C42" s="24" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="B43" s="24"/>
       <c r="C43" s="24" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="B44" s="24"/>
       <c r="C44" s="24" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="B45" s="24"/>
       <c r="C45" s="24" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="B46" s="24"/>
       <c r="C46" s="24" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="B47" s="24"/>
       <c r="C47" s="24" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="B48" s="24"/>
       <c r="C48" s="24" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="B49" s="24"/>
       <c r="C49" s="24" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="B50" s="24"/>
       <c r="C50" s="24" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="B51" s="24"/>
       <c r="C51" s="24" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="B52" s="24"/>
       <c r="C52" s="24" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
